--- a/Monitor-de-Toners-v2.0.0/Impressoras-modelo.xlsx
+++ b/Monitor-de-Toners-v2.0.0/Impressoras-modelo.xlsx
@@ -632,7 +632,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Obrigatório. Endereço da impressora na rede, por exemplo 10.162.84.144. É o único campo sem o qual a linha é ignorada.</t>
+          <t>Obrigatório. Endereço da impressora na rede, por exemplo 192.168.1.144. É o único campo sem o qual a linha é ignorada.</t>
         </is>
       </c>
     </row>
